--- a/outputs/qc/qc_bcf_quantiles.xlsx
+++ b/outputs/qc/qc_bcf_quantiles.xlsx
@@ -428,7 +428,7 @@
         <v>0.01</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001234558912753304</v>
+        <v>0.001244235255258973</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +436,7 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002929238395563136</v>
+        <v>0.002867924936924058</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +444,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.019327731092437</v>
+        <v>0.0203921568627451</v>
       </c>
     </row>
     <row r="5">
@@ -452,7 +452,7 @@
         <v>0.95</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0939445104361105</v>
+        <v>0.1410077594256094</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +460,7 @@
         <v>0.99</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1746951220929284</v>
+        <v>0.3594238310708912</v>
       </c>
     </row>
   </sheetData>
